--- a/results/andar_할인율모니터링_20260913.xlsx
+++ b/results/andar_할인율모니터링_20260913.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,12 +781,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10,093</t>
+          <t>10,094</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8,117</t>
+          <t>8,123</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>422</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1423,37 +1423,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>EOTBG-21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>데일리 라운드백</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1465,37 +1465,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EOTBG-21</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>데일리 라운드백</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1675,17 +1675,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1759,84 +1759,84 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EOTBG-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>폴더블 미니백 2.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1,141</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EOTBG-16</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>폴더블 미니백 2.0</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>1,142</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>5,133</t>
+          <t>5,135</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1969,59 +1969,59 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>EOTBG-14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>폴더블 캐리백 2.0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2031,101 +2031,101 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EOTBG-14</t>
+          <t>EOTFB-01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>폴더블 캐리백 2.0</t>
+          <t>에어쿨링 서스테이너블 와이드 헤드밴드</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>2,436</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EOTFB-01</t>
+          <t>EOTBG-19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>에어쿨링 서스테이너블 와이드 헤드밴드</t>
+          <t>위켄드 호보백</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2,433</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2137,79 +2137,79 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3,208</t>
+          <t>733</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>ENTSO-02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3,208</t>
+          <t>1,042</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2221,37 +2221,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EOTBG-19</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>위켄드 호보백</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>1,042</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2263,37 +2263,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ENTSO-02</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>[1&amp;1] 램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1,041</t>
+          <t>841</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2305,37 +2305,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1,041</t>
+          <t>3,209</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2347,17 +2347,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[1&amp;1] 램스울 크루 삭스</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>3,209</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2389,42 +2389,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3,026</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2473,331 +2473,331 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>3,026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>필라테스 크루 삭스</t>
+          <t>[1&amp;1] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>2,016</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 무릎 보호대</t>
+          <t>필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2,015</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EOTBG-17</t>
+          <t>EOTBG-23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3 in 1 캐리온 더플백</t>
+          <t>안다르 실버 리유저블백 M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTBG-17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>3 in 1 캐리온 더플백</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>109,000</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EOTBG-23</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 M</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>818</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>6,593</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>레그 숏 워머</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2809,69 +2809,69 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13843&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EOTBG-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>액티브 라이트 백팩</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>382</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>EPTET-02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>언더웨어 세탁망</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2893,27 +2893,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EOTBG-12</t>
+          <t>EOTCP-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>프리런 벨크로 러닝 벨트</t>
+          <t>올라운드 버킷햇</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>359</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2935,27 +2935,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13843&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EOTBG-02</t>
+          <t>EOTBG-12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>액티브 라이트 백팩</t>
+          <t>프리런 벨크로 러닝 벨트</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2977,27 +2977,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3007,39 +3007,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>6,593</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EPTET-02</t>
+          <t>EOTCP-05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>언더웨어 세탁망</t>
+          <t>히트 런 이어플랩 캡</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3049,39 +3049,39 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EOTSC-15</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 풀 토삭스</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3091,39 +3091,39 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EOTMK-01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>필라테스 토삭스</t>
+          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3133,39 +3133,39 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1,106</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EOTMK-01</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
+          <t>필라테스 토삭스</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3175,49 +3175,49 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1,106</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EOTSC-15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>논슬립 퍼포먼스 풀 토삭스</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3229,69 +3229,69 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EOTCP-05</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>197</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6,364</t>
+          <t>6,366</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3355,84 +3355,84 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>708</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3523,27 +3523,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EMTET-02</t>
+          <t>EPTCP-03</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>소프트 쿠셔닝 훌라후프</t>
+          <t>썬가드 와이드 버킷햇</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3553,39 +3553,39 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EMTET-02</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>소프트 쿠셔닝 훌라후프</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3595,81 +3595,81 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1,561</t>
+          <t>634</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3679,39 +3679,39 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2,116</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>696</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3733,37 +3733,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>램스울 크루 삭스</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3775,27 +3775,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ENTMK-01</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UV 프로텍션 맨즈 골프 마스크</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3805,39 +3805,39 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1,537</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>1,561</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3859,27 +3859,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>EOTSC-06</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>서포트 쿠션 러닝 삭스</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3889,39 +3889,39 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>767</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EOTMK-02</t>
+          <t>ENTMK-01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>소프텐션 넥마스크</t>
+          <t>UV 프로텍션 맨즈 골프 마스크</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>1,537</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3943,27 +3943,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EOTBG-04</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>데님 포켓 숄더백</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3973,39 +3973,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2,116</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EOTSC-06</t>
+          <t>EOTMK-02</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>서포트 쿠션 러닝 삭스</t>
+          <t>소프텐션 넥마스크</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4015,91 +4015,91 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4111,27 +4111,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 크루삭스</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4141,39 +4141,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4195,27 +4195,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4225,123 +4225,123 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>1,092</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EOTSC-13</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>테이핑 테크 러닝 삭스</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>논슬립 퍼포먼스 크루삭스</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4351,81 +4351,81 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>667</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>서포트 허리 보호대</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>35,600</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EOTSC-13</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>테이핑 테크 러닝 삭스</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4435,49 +4435,49 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>695</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>[1&amp;1] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1,092</t>
+          <t>722</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4489,69 +4489,69 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>ENTSC-20</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 발목 보호대</t>
+          <t>시그니처 로고 크루 삭스</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>583</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ENTSC-20</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>시그니처 로고 크루 삭스</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4561,123 +4561,123 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>469</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>479</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1,228</t>
+          <t>1,230</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4741,27 +4741,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>568</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4783,27 +4783,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4813,39 +4813,39 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EOTBG-11</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>메쉬 파우치</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>192</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4867,27 +4867,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4897,91 +4897,91 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1,330</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>EMTSC-17</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>[3 SET] 맨즈 클래식 삭스</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1,330</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4993,27 +4993,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5035,69 +5035,69 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EOTGL-03</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>필라테스 앵클 삭스</t>
+          <t>소프트 니트 플립 글러브</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ENTET-02</t>
+          <t>EOTBG-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 2kg</t>
+          <t>데님 포켓 숄더백</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5107,49 +5107,49 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EOTGL-03</t>
+          <t>ENTET-02</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>소프트 니트 플립 글러브</t>
+          <t>릴렉스 소프트 웨이트바 2kg</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5161,121 +5161,121 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EMTSC-17</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[3 SET] 맨즈 클래식 삭스</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20,700</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EOTBG-11</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>메쉬 파우치</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5287,111 +5287,111 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>ENTMU-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>소프트 니트 머플러</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>472</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ENTMU-01</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>소프트 니트 머플러</t>
+          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EOTSC-11</t>
+          <t>EPTCP-02</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>웜 레그 롱 워머</t>
+          <t>시그니처 로고 나일론 볼캡</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5413,69 +5413,69 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EOTSC-11</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
+          <t>웜 레그 롱 워머</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EPTCP-02</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>시그니처 로고 나일론 볼캡</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5485,39 +5485,39 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>4,136</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5527,39 +5527,39 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>4,136</t>
+          <t>527</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EMTRB-01</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>1,373</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EMTRB-01</t>
+          <t>EMTRB-02</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EMTRB-02</t>
+          <t>EMTRB-03</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5665,27 +5665,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EMTRB-03</t>
+          <t>EOTET-01</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>소프트 뱀부 롱 타월</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1,373</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5707,27 +5707,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5737,39 +5737,39 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>556</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3D 쿨링 팔토시</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5779,39 +5779,39 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ENTBG-14</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>웨이브 패딩 파우치</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5833,27 +5833,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5863,39 +5863,39 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>722</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EOTET-01</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>소프트 뱀부 롱 타월</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5905,39 +5905,39 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>708</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6001,27 +6001,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6031,49 +6031,49 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6085,79 +6085,79 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6169,27 +6169,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>ENTBG-14</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>웨이브 패딩 파우치</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6199,123 +6199,123 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EPTSC-01</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>쿨 메쉬 서포트 러닝 삭스</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6325,81 +6325,81 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EOTBO-01</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>액티브 스포츠 보틀 (650ml)</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>556</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTFB-05</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 니삭스</t>
+          <t>소프트 니트 헤드밴드</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>913</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6421,69 +6421,69 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17446&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EPTSV-01</t>
+          <t>ENTSC-26</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 핑거홀 팔토시</t>
+          <t>니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>31,800</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>26,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ENTFB-05</t>
+          <t>EOTBO-01</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>소프트 니트 헤드밴드</t>
+          <t>액티브 스포츠 보틀 (650ml)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6505,37 +6505,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>논슬립 퍼포먼스 니삭스</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>753</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6547,37 +6547,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EPTSV-02</t>
+          <t>EMTSC-27</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
+          <t>올라운드 오버 니삭스</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6589,37 +6589,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6631,69 +6631,69 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EMTSC-27</t>
+          <t>EPTSC-01</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>올라운드 오버 니삭스</t>
+          <t>쿨 메쉬 서포트 러닝 삭스</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6715,69 +6715,69 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12488&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ENTBG-10</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>스퀘어 크로스백</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6787,39 +6787,39 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12488&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EPTCP-03</t>
+          <t>ENTBG-10</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>썬가드 와이드 버킷햇</t>
+          <t>스퀘어 크로스백</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6829,39 +6829,39 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>633</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ENTFB-04</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>더블 링글 손목밴드</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6871,39 +6871,39 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>646</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>ENTFB-04</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>더블 링글 손목밴드</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>435</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2,015</t>
+          <t>2,016</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6967,27 +6967,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>ENTCP-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>서포트 팔꿈치 보호대</t>
+          <t>와이드 셰이드 버킷햇</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>686</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7009,27 +7009,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ENTSC-26</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>니트 기모 오버 니삭스</t>
+          <t>서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -7219,27 +7219,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>ENTCP-05</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>하이 서포트 팔꿈치 보호대</t>
+          <t>소프트 니트 비니</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7249,39 +7249,39 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ENTCP-05</t>
+          <t>EMTSC-29</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>소프트 니트 비니</t>
+          <t>니트 루즈 삭스</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7291,39 +7291,39 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EMTSC-29</t>
+          <t>EOTCP-02</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>니트 루즈 삭스</t>
+          <t>데님 로고 볼캡</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7345,27 +7345,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EOTCP-02</t>
+          <t>ENTSC-05</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>데님 로고 볼캡</t>
+          <t>에어프레시 크루 삭스</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>575</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7387,27 +7387,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16636&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ENTSC-05</t>
+          <t>EPTFB-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>에어프레시 크루 삭스</t>
+          <t>퍼포먼스 심리스 헤드밴드</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7429,27 +7429,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7459,39 +7459,39 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16636&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EPTFB-01</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 헤드밴드</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -7849,27 +7849,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ENTCP-01</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>와이드 셰이드 버킷햇</t>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7879,52 +7879,10 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>EKPET-01</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>릴렉스 소프트 웨이트바 1kg</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>20,900</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>20,900</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
